--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:53:23+00:00</t>
+    <t>2026-09-18T08:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:26:19+00:00</t>
+    <t>2026-09-24T07:33:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$268</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$274</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9890" uniqueCount="907">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10109" uniqueCount="925">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T07:33:45+00:00</t>
+    <t>2026-09-30T20:06:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2474,6 +2474,10 @@
     <t>Provides context for the composition and creates a linkage between a resource describing an event and the composition created describing the event.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:extension('https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-is-principal-event-extension').value}
+</t>
+  </si>
+  <si>
     <t>outboundRelationship[typeCode="SUBJ"].target[classCode&lt;'ACT']</t>
   </si>
   <si>
@@ -2505,6 +2509,22 @@
     <t>Extension permettant d'ajouter l'exécutant de l'évènement documenté. Ajout d'un performer à l'élément event d'une Composition.</t>
   </si>
   <si>
+    <t>Composition.event.extension:isPrincipal</t>
+  </si>
+  <si>
+    <t>isPrincipal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-is-principal-event-extension|0.1.0}
+</t>
+  </si>
+  <si>
+    <t>Indique si l'évènement documenté est l'évènement principal</t>
+  </si>
+  <si>
+    <t>Extension permettant d'indiquer si l'évènement documenté est l'évènement documenté principal. Vaut true pour l'évènement principal. Ajout d'un indicateur à l'élément event d'une Composition.</t>
+  </si>
+  <si>
     <t>Composition.event.modifierExtension</t>
   </si>
   <si>
@@ -2578,6 +2598,43 @@
     <t>Exécutant de l'évènement documenté principal</t>
   </si>
   <si>
+    <t>Composition.event:principalEvent.extension:isPrincipal</t>
+  </si>
+  <si>
+    <t>Composition.event:principalEvent.extension:isPrincipal.id</t>
+  </si>
+  <si>
+    <t>Composition.event.extension.id</t>
+  </si>
+  <si>
+    <t>Composition.event:principalEvent.extension:isPrincipal.extension</t>
+  </si>
+  <si>
+    <t>Composition.event.extension.extension</t>
+  </si>
+  <si>
+    <t>Composition.event:principalEvent.extension:isPrincipal.url</t>
+  </si>
+  <si>
+    <t>Composition.event.extension.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-is-principal-event-extension</t>
+  </si>
+  <si>
+    <t>Composition.event:principalEvent.extension:isPrincipal.value[x]</t>
+  </si>
+  <si>
+    <t>Composition.event.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
     <t>Composition.event:principalEvent.modifierExtension</t>
   </si>
   <si>
@@ -2603,7 +2660,7 @@
   </si>
   <si>
     <t>cmp-1:A section must contain at least one of text, entries, or sub-sections {text.exists() or entry.exists() or section.exists()}
-cmp-2:A section can only have an emptyReason if it is empty {emptyReason.empty() or entry.empty()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}comp-4:Une section ne peut pas contenir à la fois des entrées et des sous-sections. {not(exists(f:entry) and exists(f:section))}</t>
+cmp-2:A section can only have an emptyReason if it is empty {emptyReason.empty() or entry.empty()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}comp-4:Une section ne peut pas contenir à la fois des entrées et des sous-sections. {entry.exists().not() or section.exists().not()}</t>
   </si>
   <si>
     <t>./outboundRelationship[typeCode="COMP" and isNormalActRelationship()]/target[moodCode="EVN" and classCode="DOCSECT" and isNormalAct]</t>
@@ -2681,7 +2738,7 @@
     <t>Provides computable standardized labels to topics within the document.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-section-document-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-section-document-cisis|20260916095455</t>
   </si>
   <si>
     <t>Composition.section.author</t>
@@ -3154,7 +3211,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO268"/>
+  <dimension ref="A1:AO274"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="67.234375" customWidth="true" bestFit="true"/>
@@ -3184,7 +3241,7 @@
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="89.12890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="101.734375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -30770,7 +30827,7 @@
         <v>78</v>
       </c>
       <c r="AB237" t="s" s="2">
-        <v>143</v>
+        <v>788</v>
       </c>
       <c r="AC237" s="2"/>
       <c r="AD237" t="s" s="2">
@@ -30798,13 +30855,13 @@
         <v>78</v>
       </c>
       <c r="AL237" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AM237" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AN237" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AO237" t="s" s="2">
         <v>78</v>
@@ -30812,10 +30869,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -30927,10 +30984,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -31040,13 +31097,13 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="B240" t="s" s="2">
         <v>793</v>
       </c>
-      <c r="B240" t="s" s="2">
-        <v>792</v>
-      </c>
       <c r="C240" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D240" t="s" s="2">
         <v>78</v>
@@ -31068,13 +31125,13 @@
         <v>78</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N240" s="2"/>
       <c r="O240" s="2"/>
@@ -31157,46 +31214,44 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>798</v>
-      </c>
-      <c r="C241" s="2"/>
+        <v>793</v>
+      </c>
+      <c r="C241" t="s" s="2">
+        <v>800</v>
+      </c>
       <c r="D241" t="s" s="2">
-        <v>595</v>
+        <v>78</v>
       </c>
       <c r="E241" s="2"/>
       <c r="F241" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G241" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H241" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I241" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="J241" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>112</v>
+        <v>801</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>596</v>
+        <v>802</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N241" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O241" t="s" s="2">
-        <v>427</v>
-      </c>
+        <v>803</v>
+      </c>
+      <c r="N241" s="2"/>
+      <c r="O241" s="2"/>
       <c r="P241" t="s" s="2">
         <v>78</v>
       </c>
@@ -31244,7 +31299,7 @@
         <v>78</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>598</v>
+        <v>119</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>79</v>
@@ -31253,7 +31308,7 @@
         <v>80</v>
       </c>
       <c r="AI241" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ241" t="s" s="2">
         <v>120</v>
@@ -31262,7 +31317,7 @@
         <v>78</v>
       </c>
       <c r="AL241" t="s" s="2">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="AM241" t="s" s="2">
         <v>78</v>
@@ -31276,14 +31331,14 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
-        <v>78</v>
+        <v>595</v>
       </c>
       <c r="E242" s="2"/>
       <c r="F242" t="s" s="2">
@@ -31296,24 +31351,26 @@
         <v>78</v>
       </c>
       <c r="I242" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="J242" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>237</v>
+        <v>112</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>800</v>
+        <v>596</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>801</v>
+        <v>597</v>
       </c>
       <c r="N242" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="O242" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="O242" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="P242" t="s" s="2">
         <v>78</v>
       </c>
@@ -31337,13 +31394,13 @@
         <v>78</v>
       </c>
       <c r="X242" t="s" s="2">
-        <v>163</v>
+        <v>78</v>
       </c>
       <c r="Y242" t="s" s="2">
-        <v>803</v>
+        <v>78</v>
       </c>
       <c r="Z242" t="s" s="2">
-        <v>804</v>
+        <v>78</v>
       </c>
       <c r="AA242" t="s" s="2">
         <v>78</v>
@@ -31361,7 +31418,7 @@
         <v>78</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>799</v>
+        <v>598</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>79</v>
@@ -31373,19 +31430,19 @@
         <v>78</v>
       </c>
       <c r="AJ242" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK242" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL242" t="s" s="2">
-        <v>472</v>
+        <v>197</v>
       </c>
       <c r="AM242" t="s" s="2">
-        <v>472</v>
+        <v>78</v>
       </c>
       <c r="AN242" t="s" s="2">
-        <v>805</v>
+        <v>78</v>
       </c>
       <c r="AO242" t="s" s="2">
         <v>78</v>
@@ -31393,10 +31450,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -31407,7 +31464,7 @@
         <v>79</v>
       </c>
       <c r="G243" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H243" t="s" s="2">
         <v>78</v>
@@ -31419,15 +31476,17 @@
         <v>92</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="L243" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="M243" t="s" s="2">
         <v>807</v>
       </c>
-      <c r="M243" t="s" s="2">
+      <c r="N243" t="s" s="2">
         <v>808</v>
       </c>
-      <c r="N243" s="2"/>
       <c r="O243" s="2"/>
       <c r="P243" t="s" s="2">
         <v>78</v>
@@ -31452,13 +31511,13 @@
         <v>78</v>
       </c>
       <c r="X243" t="s" s="2">
-        <v>78</v>
+        <v>163</v>
       </c>
       <c r="Y243" t="s" s="2">
-        <v>78</v>
+        <v>809</v>
       </c>
       <c r="Z243" t="s" s="2">
-        <v>78</v>
+        <v>810</v>
       </c>
       <c r="AA243" t="s" s="2">
         <v>78</v>
@@ -31476,13 +31535,13 @@
         <v>78</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH243" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI243" t="s" s="2">
         <v>78</v>
@@ -31494,13 +31553,13 @@
         <v>78</v>
       </c>
       <c r="AL243" t="s" s="2">
-        <v>543</v>
+        <v>472</v>
       </c>
       <c r="AM243" t="s" s="2">
-        <v>543</v>
+        <v>472</v>
       </c>
       <c r="AN243" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="AO243" t="s" s="2">
         <v>78</v>
@@ -31508,10 +31567,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -31534,13 +31593,13 @@
         <v>92</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>811</v>
+        <v>261</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="N244" s="2"/>
       <c r="O244" s="2"/>
@@ -31591,13 +31650,13 @@
         <v>78</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH244" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI244" t="s" s="2">
         <v>78</v>
@@ -31609,13 +31668,13 @@
         <v>78</v>
       </c>
       <c r="AL244" t="s" s="2">
-        <v>814</v>
+        <v>543</v>
       </c>
       <c r="AM244" t="s" s="2">
-        <v>109</v>
+        <v>543</v>
       </c>
       <c r="AN244" t="s" s="2">
-        <v>78</v>
+        <v>815</v>
       </c>
       <c r="AO244" t="s" s="2">
         <v>78</v>
@@ -31623,20 +31682,18 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="C245" t="s" s="2">
         <v>816</v>
       </c>
+      <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E245" s="2"/>
       <c r="F245" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G245" t="s" s="2">
         <v>91</v>
@@ -31651,20 +31708,16 @@
         <v>92</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>582</v>
+        <v>817</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="N245" t="s" s="2">
-        <v>786</v>
-      </c>
-      <c r="O245" t="s" s="2">
-        <v>787</v>
-      </c>
+        <v>819</v>
+      </c>
+      <c r="N245" s="2"/>
+      <c r="O245" s="2"/>
       <c r="P245" t="s" s="2">
         <v>78</v>
       </c>
@@ -31712,7 +31765,7 @@
         <v>78</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>783</v>
+        <v>816</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>79</v>
@@ -31730,13 +31783,13 @@
         <v>78</v>
       </c>
       <c r="AL245" t="s" s="2">
-        <v>788</v>
+        <v>820</v>
       </c>
       <c r="AM245" t="s" s="2">
-        <v>789</v>
+        <v>109</v>
       </c>
       <c r="AN245" t="s" s="2">
-        <v>790</v>
+        <v>78</v>
       </c>
       <c r="AO245" t="s" s="2">
         <v>78</v>
@@ -31744,18 +31797,20 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>791</v>
-      </c>
-      <c r="C246" s="2"/>
+        <v>783</v>
+      </c>
+      <c r="C246" t="s" s="2">
+        <v>822</v>
+      </c>
       <c r="D246" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E246" s="2"/>
       <c r="F246" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G246" t="s" s="2">
         <v>91</v>
@@ -31767,19 +31822,23 @@
         <v>78</v>
       </c>
       <c r="J246" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>105</v>
+        <v>582</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>106</v>
+        <v>823</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N246" s="2"/>
-      <c r="O246" s="2"/>
+        <v>785</v>
+      </c>
+      <c r="N246" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="O246" t="s" s="2">
+        <v>787</v>
+      </c>
       <c r="P246" t="s" s="2">
         <v>78</v>
       </c>
@@ -31827,31 +31886,31 @@
         <v>78</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>108</v>
+        <v>783</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH246" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI246" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ246" t="s" s="2">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="AK246" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL246" t="s" s="2">
-        <v>109</v>
+        <v>789</v>
       </c>
       <c r="AM246" t="s" s="2">
-        <v>78</v>
+        <v>790</v>
       </c>
       <c r="AN246" t="s" s="2">
-        <v>78</v>
+        <v>791</v>
       </c>
       <c r="AO246" t="s" s="2">
         <v>78</v>
@@ -31859,7 +31918,7 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="B247" t="s" s="2">
         <v>792</v>
@@ -31870,10 +31929,10 @@
       </c>
       <c r="E247" s="2"/>
       <c r="F247" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G247" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H247" t="s" s="2">
         <v>78</v>
@@ -31885,13 +31944,13 @@
         <v>78</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>199</v>
+        <v>106</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>200</v>
+        <v>107</v>
       </c>
       <c r="N247" s="2"/>
       <c r="O247" s="2"/>
@@ -31930,35 +31989,37 @@
         <v>78</v>
       </c>
       <c r="AB247" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC247" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC247" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD247" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE247" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH247" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI247" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ247" t="s" s="2">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="AK247" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL247" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="AM247" t="s" s="2">
         <v>78</v>
@@ -31972,23 +32033,21 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>792</v>
-      </c>
-      <c r="C248" t="s" s="2">
-        <v>794</v>
-      </c>
+        <v>793</v>
+      </c>
+      <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E248" s="2"/>
       <c r="F248" t="s" s="2">
-        <v>91</v>
+        <v>283</v>
       </c>
       <c r="G248" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H248" t="s" s="2">
         <v>78</v>
@@ -32000,13 +32059,13 @@
         <v>78</v>
       </c>
       <c r="K248" t="s" s="2">
-        <v>795</v>
+        <v>112</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>821</v>
+        <v>199</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>797</v>
+        <v>200</v>
       </c>
       <c r="N248" s="2"/>
       <c r="O248" s="2"/>
@@ -32045,16 +32104,14 @@
         <v>78</v>
       </c>
       <c r="AB248" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC248" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="AC248" s="2"/>
       <c r="AD248" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE248" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AF248" t="s" s="2">
         <v>119</v>
@@ -32066,7 +32123,7 @@
         <v>80</v>
       </c>
       <c r="AI248" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ248" t="s" s="2">
         <v>120</v>
@@ -32089,46 +32146,44 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>798</v>
-      </c>
-      <c r="C249" s="2"/>
+        <v>793</v>
+      </c>
+      <c r="C249" t="s" s="2">
+        <v>795</v>
+      </c>
       <c r="D249" t="s" s="2">
-        <v>595</v>
+        <v>78</v>
       </c>
       <c r="E249" s="2"/>
       <c r="F249" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G249" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H249" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I249" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="J249" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>112</v>
+        <v>796</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>596</v>
+        <v>827</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N249" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O249" t="s" s="2">
-        <v>427</v>
-      </c>
+        <v>798</v>
+      </c>
+      <c r="N249" s="2"/>
+      <c r="O249" s="2"/>
       <c r="P249" t="s" s="2">
         <v>78</v>
       </c>
@@ -32176,7 +32231,7 @@
         <v>78</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>598</v>
+        <v>119</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>79</v>
@@ -32185,7 +32240,7 @@
         <v>80</v>
       </c>
       <c r="AI249" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ249" t="s" s="2">
         <v>120</v>
@@ -32194,7 +32249,7 @@
         <v>78</v>
       </c>
       <c r="AL249" t="s" s="2">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="AM249" t="s" s="2">
         <v>78</v>
@@ -32208,21 +32263,23 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>799</v>
-      </c>
-      <c r="C250" s="2"/>
+        <v>793</v>
+      </c>
+      <c r="C250" t="s" s="2">
+        <v>800</v>
+      </c>
       <c r="D250" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E250" s="2"/>
       <c r="F250" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G250" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H250" t="s" s="2">
         <v>78</v>
@@ -32231,20 +32288,18 @@
         <v>78</v>
       </c>
       <c r="J250" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="K250" t="s" s="2">
-        <v>237</v>
+        <v>801</v>
       </c>
       <c r="L250" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="M250" t="s" s="2">
-        <v>801</v>
-      </c>
-      <c r="N250" t="s" s="2">
-        <v>802</v>
-      </c>
+        <v>803</v>
+      </c>
+      <c r="N250" s="2"/>
       <c r="O250" s="2"/>
       <c r="P250" t="s" s="2">
         <v>78</v>
@@ -32269,13 +32324,13 @@
         <v>78</v>
       </c>
       <c r="X250" t="s" s="2">
-        <v>163</v>
+        <v>78</v>
       </c>
       <c r="Y250" t="s" s="2">
-        <v>803</v>
+        <v>78</v>
       </c>
       <c r="Z250" t="s" s="2">
-        <v>804</v>
+        <v>78</v>
       </c>
       <c r="AA250" t="s" s="2">
         <v>78</v>
@@ -32293,7 +32348,7 @@
         <v>78</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>799</v>
+        <v>119</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>79</v>
@@ -32302,22 +32357,22 @@
         <v>80</v>
       </c>
       <c r="AI250" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ250" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK250" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL250" t="s" s="2">
-        <v>472</v>
+        <v>78</v>
       </c>
       <c r="AM250" t="s" s="2">
-        <v>472</v>
+        <v>78</v>
       </c>
       <c r="AN250" t="s" s="2">
-        <v>805</v>
+        <v>78</v>
       </c>
       <c r="AO250" t="s" s="2">
         <v>78</v>
@@ -32325,10 +32380,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>806</v>
+        <v>830</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -32336,7 +32391,7 @@
       </c>
       <c r="E251" s="2"/>
       <c r="F251" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G251" t="s" s="2">
         <v>91</v>
@@ -32348,16 +32403,16 @@
         <v>78</v>
       </c>
       <c r="J251" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="K251" t="s" s="2">
-        <v>261</v>
+        <v>105</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>825</v>
+        <v>106</v>
       </c>
       <c r="M251" t="s" s="2">
-        <v>808</v>
+        <v>107</v>
       </c>
       <c r="N251" s="2"/>
       <c r="O251" s="2"/>
@@ -32408,7 +32463,7 @@
         <v>78</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>806</v>
+        <v>108</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>79</v>
@@ -32420,19 +32475,19 @@
         <v>78</v>
       </c>
       <c r="AJ251" t="s" s="2">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="AK251" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL251" t="s" s="2">
-        <v>543</v>
+        <v>109</v>
       </c>
       <c r="AM251" t="s" s="2">
-        <v>543</v>
+        <v>78</v>
       </c>
       <c r="AN251" t="s" s="2">
-        <v>809</v>
+        <v>78</v>
       </c>
       <c r="AO251" t="s" s="2">
         <v>78</v>
@@ -32440,10 +32495,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>810</v>
+        <v>832</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -32454,7 +32509,7 @@
         <v>79</v>
       </c>
       <c r="G252" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H252" t="s" s="2">
         <v>78</v>
@@ -32463,16 +32518,16 @@
         <v>78</v>
       </c>
       <c r="J252" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>811</v>
+        <v>112</v>
       </c>
       <c r="L252" t="s" s="2">
-        <v>812</v>
+        <v>199</v>
       </c>
       <c r="M252" t="s" s="2">
-        <v>813</v>
+        <v>200</v>
       </c>
       <c r="N252" s="2"/>
       <c r="O252" s="2"/>
@@ -32511,19 +32566,19 @@
         <v>78</v>
       </c>
       <c r="AB252" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AC252" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AD252" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE252" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AF252" t="s" s="2">
-        <v>810</v>
+        <v>119</v>
       </c>
       <c r="AG252" t="s" s="2">
         <v>79</v>
@@ -32535,16 +32590,16 @@
         <v>78</v>
       </c>
       <c r="AJ252" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK252" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL252" t="s" s="2">
-        <v>814</v>
+        <v>78</v>
       </c>
       <c r="AM252" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="AN252" t="s" s="2">
         <v>78</v>
@@ -32553,12 +32608,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -32569,10 +32624,10 @@
         <v>91</v>
       </c>
       <c r="G253" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H253" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I253" t="s" s="2">
         <v>78</v>
@@ -32581,22 +32636,24 @@
         <v>78</v>
       </c>
       <c r="K253" t="s" s="2">
-        <v>582</v>
+        <v>133</v>
       </c>
       <c r="L253" t="s" s="2">
-        <v>828</v>
+        <v>231</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>829</v>
-      </c>
-      <c r="N253" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N253" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="O253" s="2"/>
       <c r="P253" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q253" s="2"/>
       <c r="R253" t="s" s="2">
-        <v>78</v>
+        <v>835</v>
       </c>
       <c r="S253" t="s" s="2">
         <v>78</v>
@@ -32638,28 +32695,28 @@
         <v>78</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>827</v>
+        <v>234</v>
       </c>
       <c r="AG253" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH253" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI253" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ253" t="s" s="2">
-        <v>830</v>
+        <v>78</v>
       </c>
       <c r="AK253" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL253" t="s" s="2">
-        <v>831</v>
+        <v>197</v>
       </c>
       <c r="AM253" t="s" s="2">
-        <v>832</v>
+        <v>78</v>
       </c>
       <c r="AN253" t="s" s="2">
         <v>78</v>
@@ -32670,10 +32727,10 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -32681,7 +32738,7 @@
       </c>
       <c r="E254" s="2"/>
       <c r="F254" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G254" t="s" s="2">
         <v>91</v>
@@ -32696,13 +32753,13 @@
         <v>78</v>
       </c>
       <c r="K254" t="s" s="2">
-        <v>105</v>
+        <v>838</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="M254" t="s" s="2">
-        <v>107</v>
+        <v>239</v>
       </c>
       <c r="N254" s="2"/>
       <c r="O254" s="2"/>
@@ -32714,7 +32771,7 @@
         <v>78</v>
       </c>
       <c r="S254" t="s" s="2">
-        <v>78</v>
+        <v>839</v>
       </c>
       <c r="T254" t="s" s="2">
         <v>78</v>
@@ -32753,7 +32810,7 @@
         <v>78</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>108</v>
+        <v>242</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>79</v>
@@ -32765,13 +32822,13 @@
         <v>78</v>
       </c>
       <c r="AJ254" t="s" s="2">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="AK254" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL254" t="s" s="2">
-        <v>109</v>
+        <v>197</v>
       </c>
       <c r="AM254" t="s" s="2">
         <v>78</v>
@@ -32785,14 +32842,14 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>834</v>
+        <v>804</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
-        <v>78</v>
+        <v>595</v>
       </c>
       <c r="E255" s="2"/>
       <c r="F255" t="s" s="2">
@@ -32805,22 +32862,26 @@
         <v>78</v>
       </c>
       <c r="I255" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="J255" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="K255" t="s" s="2">
         <v>112</v>
       </c>
       <c r="L255" t="s" s="2">
-        <v>199</v>
+        <v>596</v>
       </c>
       <c r="M255" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N255" s="2"/>
-      <c r="O255" s="2"/>
+        <v>597</v>
+      </c>
+      <c r="N255" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O255" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="P255" t="s" s="2">
         <v>78</v>
       </c>
@@ -32856,17 +32917,19 @@
         <v>78</v>
       </c>
       <c r="AB255" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC255" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC255" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD255" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE255" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>119</v>
+        <v>598</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>79</v>
@@ -32884,7 +32947,7 @@
         <v>78</v>
       </c>
       <c r="AL255" t="s" s="2">
-        <v>78</v>
+        <v>197</v>
       </c>
       <c r="AM255" t="s" s="2">
         <v>78</v>
@@ -32898,14 +32961,12 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>834</v>
-      </c>
-      <c r="C256" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>805</v>
+      </c>
+      <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
         <v>78</v>
       </c>
@@ -32914,7 +32975,7 @@
         <v>79</v>
       </c>
       <c r="G256" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H256" t="s" s="2">
         <v>78</v>
@@ -32923,18 +32984,20 @@
         <v>78</v>
       </c>
       <c r="J256" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="K256" t="s" s="2">
-        <v>409</v>
+        <v>237</v>
       </c>
       <c r="L256" t="s" s="2">
-        <v>836</v>
+        <v>806</v>
       </c>
       <c r="M256" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N256" s="2"/>
+        <v>807</v>
+      </c>
+      <c r="N256" t="s" s="2">
+        <v>808</v>
+      </c>
       <c r="O256" s="2"/>
       <c r="P256" t="s" s="2">
         <v>78</v>
@@ -32959,13 +33022,13 @@
         <v>78</v>
       </c>
       <c r="X256" t="s" s="2">
-        <v>78</v>
+        <v>163</v>
       </c>
       <c r="Y256" t="s" s="2">
-        <v>78</v>
+        <v>809</v>
       </c>
       <c r="Z256" t="s" s="2">
-        <v>78</v>
+        <v>810</v>
       </c>
       <c r="AA256" t="s" s="2">
         <v>78</v>
@@ -32983,7 +33046,7 @@
         <v>78</v>
       </c>
       <c r="AF256" t="s" s="2">
-        <v>119</v>
+        <v>805</v>
       </c>
       <c r="AG256" t="s" s="2">
         <v>79</v>
@@ -32992,22 +33055,22 @@
         <v>80</v>
       </c>
       <c r="AI256" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ256" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK256" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL256" t="s" s="2">
-        <v>78</v>
+        <v>472</v>
       </c>
       <c r="AM256" t="s" s="2">
-        <v>78</v>
+        <v>472</v>
       </c>
       <c r="AN256" t="s" s="2">
-        <v>78</v>
+        <v>811</v>
       </c>
       <c r="AO256" t="s" s="2">
         <v>78</v>
@@ -33015,23 +33078,21 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>834</v>
-      </c>
-      <c r="C257" t="s" s="2">
-        <v>838</v>
-      </c>
+        <v>812</v>
+      </c>
+      <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E257" s="2"/>
       <c r="F257" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G257" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H257" t="s" s="2">
         <v>78</v>
@@ -33040,20 +33101,18 @@
         <v>78</v>
       </c>
       <c r="J257" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="K257" t="s" s="2">
-        <v>839</v>
+        <v>261</v>
       </c>
       <c r="L257" t="s" s="2">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>841</v>
-      </c>
-      <c r="N257" t="s" s="2">
-        <v>842</v>
-      </c>
+        <v>814</v>
+      </c>
+      <c r="N257" s="2"/>
       <c r="O257" s="2"/>
       <c r="P257" t="s" s="2">
         <v>78</v>
@@ -33102,31 +33161,31 @@
         <v>78</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>119</v>
+        <v>812</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH257" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI257" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ257" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK257" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL257" t="s" s="2">
-        <v>78</v>
+        <v>543</v>
       </c>
       <c r="AM257" t="s" s="2">
-        <v>78</v>
+        <v>543</v>
       </c>
       <c r="AN257" t="s" s="2">
-        <v>78</v>
+        <v>815</v>
       </c>
       <c r="AO257" t="s" s="2">
         <v>78</v>
@@ -33134,46 +33193,42 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>843</v>
+        <v>816</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
-        <v>595</v>
+        <v>78</v>
       </c>
       <c r="E258" s="2"/>
       <c r="F258" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G258" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H258" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I258" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="J258" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K258" t="s" s="2">
-        <v>112</v>
+        <v>817</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>596</v>
+        <v>818</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N258" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O258" t="s" s="2">
-        <v>427</v>
-      </c>
+        <v>819</v>
+      </c>
+      <c r="N258" s="2"/>
+      <c r="O258" s="2"/>
       <c r="P258" t="s" s="2">
         <v>78</v>
       </c>
@@ -33221,7 +33276,7 @@
         <v>78</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>598</v>
+        <v>816</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>79</v>
@@ -33233,16 +33288,16 @@
         <v>78</v>
       </c>
       <c r="AJ258" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK258" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL258" t="s" s="2">
-        <v>197</v>
+        <v>820</v>
       </c>
       <c r="AM258" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="AN258" t="s" s="2">
         <v>78</v>
@@ -33253,21 +33308,21 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
-        <v>845</v>
+        <v>78</v>
       </c>
       <c r="E259" s="2"/>
       <c r="F259" t="s" s="2">
         <v>91</v>
       </c>
       <c r="G259" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H259" t="s" s="2">
         <v>92</v>
@@ -33279,7 +33334,7 @@
         <v>78</v>
       </c>
       <c r="K259" t="s" s="2">
-        <v>105</v>
+        <v>582</v>
       </c>
       <c r="L259" t="s" s="2">
         <v>846</v>
@@ -33287,12 +33342,8 @@
       <c r="M259" t="s" s="2">
         <v>847</v>
       </c>
-      <c r="N259" t="s" s="2">
-        <v>848</v>
-      </c>
-      <c r="O259" t="s" s="2">
-        <v>849</v>
-      </c>
+      <c r="N259" s="2"/>
+      <c r="O259" s="2"/>
       <c r="P259" t="s" s="2">
         <v>78</v>
       </c>
@@ -33340,28 +33391,28 @@
         <v>78</v>
       </c>
       <c r="AF259" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AG259" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH259" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI259" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ259" t="s" s="2">
-        <v>103</v>
+        <v>848</v>
       </c>
       <c r="AK259" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL259" t="s" s="2">
-        <v>570</v>
+        <v>849</v>
       </c>
       <c r="AM259" t="s" s="2">
-        <v>571</v>
+        <v>850</v>
       </c>
       <c r="AN259" t="s" s="2">
         <v>78</v>
@@ -33370,12 +33421,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="260">
+    <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -33383,13 +33434,13 @@
       </c>
       <c r="E260" s="2"/>
       <c r="F260" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G260" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H260" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I260" t="s" s="2">
         <v>78</v>
@@ -33398,20 +33449,16 @@
         <v>78</v>
       </c>
       <c r="K260" t="s" s="2">
-        <v>237</v>
+        <v>105</v>
       </c>
       <c r="L260" t="s" s="2">
-        <v>851</v>
+        <v>106</v>
       </c>
       <c r="M260" t="s" s="2">
-        <v>852</v>
-      </c>
-      <c r="N260" t="s" s="2">
-        <v>853</v>
-      </c>
-      <c r="O260" t="s" s="2">
-        <v>854</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N260" s="2"/>
+      <c r="O260" s="2"/>
       <c r="P260" t="s" s="2">
         <v>78</v>
       </c>
@@ -33435,11 +33482,13 @@
         <v>78</v>
       </c>
       <c r="X260" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="Y260" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y260" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z260" t="s" s="2">
-        <v>855</v>
+        <v>78</v>
       </c>
       <c r="AA260" t="s" s="2">
         <v>78</v>
@@ -33457,7 +33506,7 @@
         <v>78</v>
       </c>
       <c r="AF260" t="s" s="2">
-        <v>850</v>
+        <v>108</v>
       </c>
       <c r="AG260" t="s" s="2">
         <v>79</v>
@@ -33469,16 +33518,16 @@
         <v>78</v>
       </c>
       <c r="AJ260" t="s" s="2">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="AK260" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL260" t="s" s="2">
-        <v>471</v>
+        <v>109</v>
       </c>
       <c r="AM260" t="s" s="2">
-        <v>472</v>
+        <v>78</v>
       </c>
       <c r="AN260" t="s" s="2">
         <v>78</v>
@@ -33489,10 +33538,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -33515,18 +33564,16 @@
         <v>78</v>
       </c>
       <c r="K261" t="s" s="2">
-        <v>857</v>
+        <v>112</v>
       </c>
       <c r="L261" t="s" s="2">
-        <v>858</v>
+        <v>199</v>
       </c>
       <c r="M261" t="s" s="2">
-        <v>859</v>
+        <v>200</v>
       </c>
       <c r="N261" s="2"/>
-      <c r="O261" t="s" s="2">
-        <v>550</v>
-      </c>
+      <c r="O261" s="2"/>
       <c r="P261" t="s" s="2">
         <v>78</v>
       </c>
@@ -33562,19 +33609,17 @@
         <v>78</v>
       </c>
       <c r="AB261" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC261" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="AC261" s="2"/>
       <c r="AD261" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE261" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AF261" t="s" s="2">
-        <v>856</v>
+        <v>119</v>
       </c>
       <c r="AG261" t="s" s="2">
         <v>79</v>
@@ -33586,32 +33631,34 @@
         <v>78</v>
       </c>
       <c r="AJ261" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK261" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL261" t="s" s="2">
-        <v>552</v>
+        <v>78</v>
       </c>
       <c r="AM261" t="s" s="2">
-        <v>553</v>
+        <v>78</v>
       </c>
       <c r="AN261" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO261" t="s" s="2">
-        <v>555</v>
+        <v>78</v>
       </c>
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="C262" s="2"/>
+        <v>852</v>
+      </c>
+      <c r="C262" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="D262" t="s" s="2">
         <v>78</v>
       </c>
@@ -33632,17 +33679,15 @@
         <v>78</v>
       </c>
       <c r="K262" t="s" s="2">
-        <v>811</v>
+        <v>409</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="M262" t="s" s="2">
-        <v>862</v>
-      </c>
-      <c r="N262" t="s" s="2">
-        <v>863</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="N262" s="2"/>
       <c r="O262" s="2"/>
       <c r="P262" t="s" s="2">
         <v>78</v>
@@ -33691,19 +33736,19 @@
         <v>78</v>
       </c>
       <c r="AF262" t="s" s="2">
-        <v>860</v>
+        <v>119</v>
       </c>
       <c r="AG262" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH262" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI262" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ262" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK262" t="s" s="2">
         <v>78</v>
@@ -33712,7 +33757,7 @@
         <v>78</v>
       </c>
       <c r="AM262" t="s" s="2">
-        <v>864</v>
+        <v>78</v>
       </c>
       <c r="AN262" t="s" s="2">
         <v>78</v>
@@ -33721,26 +33766,28 @@
         <v>78</v>
       </c>
     </row>
-    <row r="263">
+    <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>865</v>
+        <v>855</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="C263" s="2"/>
+        <v>852</v>
+      </c>
+      <c r="C263" t="s" s="2">
+        <v>856</v>
+      </c>
       <c r="D263" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E263" s="2"/>
       <c r="F263" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G263" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H263" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I263" t="s" s="2">
         <v>78</v>
@@ -33749,16 +33796,16 @@
         <v>78</v>
       </c>
       <c r="K263" t="s" s="2">
-        <v>184</v>
+        <v>857</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="N263" t="s" s="2">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="O263" s="2"/>
       <c r="P263" t="s" s="2">
@@ -33808,28 +33855,28 @@
         <v>78</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>865</v>
+        <v>119</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH263" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI263" t="s" s="2">
-        <v>869</v>
+        <v>78</v>
       </c>
       <c r="AJ263" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK263" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL263" t="s" s="2">
-        <v>870</v>
+        <v>78</v>
       </c>
       <c r="AM263" t="s" s="2">
-        <v>870</v>
+        <v>78</v>
       </c>
       <c r="AN263" t="s" s="2">
         <v>78</v>
@@ -33840,45 +33887,45 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>871</v>
+        <v>861</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>871</v>
+        <v>861</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
-        <v>78</v>
+        <v>595</v>
       </c>
       <c r="E264" s="2"/>
       <c r="F264" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G264" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H264" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I264" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="J264" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="K264" t="s" s="2">
-        <v>173</v>
+        <v>112</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>872</v>
+        <v>596</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>873</v>
+        <v>597</v>
       </c>
       <c r="N264" t="s" s="2">
-        <v>874</v>
+        <v>115</v>
       </c>
       <c r="O264" t="s" s="2">
-        <v>875</v>
+        <v>427</v>
       </c>
       <c r="P264" t="s" s="2">
         <v>78</v>
@@ -33903,13 +33950,13 @@
         <v>78</v>
       </c>
       <c r="X264" t="s" s="2">
-        <v>327</v>
+        <v>78</v>
       </c>
       <c r="Y264" t="s" s="2">
-        <v>876</v>
+        <v>78</v>
       </c>
       <c r="Z264" t="s" s="2">
-        <v>877</v>
+        <v>78</v>
       </c>
       <c r="AA264" t="s" s="2">
         <v>78</v>
@@ -33927,56 +33974,56 @@
         <v>78</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>871</v>
+        <v>598</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH264" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI264" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ264" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK264" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL264" t="s" s="2">
-        <v>878</v>
+        <v>197</v>
       </c>
       <c r="AM264" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="AN264" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO264" t="s" s="2">
-        <v>474</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="265" hidden="true">
+    <row r="265">
       <c r="A265" t="s" s="2">
-        <v>879</v>
+        <v>862</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>879</v>
+        <v>862</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
-        <v>78</v>
+        <v>863</v>
       </c>
       <c r="E265" s="2"/>
       <c r="F265" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G265" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H265" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I265" t="s" s="2">
         <v>78</v>
@@ -33985,19 +34032,19 @@
         <v>78</v>
       </c>
       <c r="K265" t="s" s="2">
-        <v>237</v>
+        <v>105</v>
       </c>
       <c r="L265" t="s" s="2">
-        <v>880</v>
+        <v>864</v>
       </c>
       <c r="M265" t="s" s="2">
-        <v>881</v>
+        <v>865</v>
       </c>
       <c r="N265" t="s" s="2">
-        <v>882</v>
+        <v>866</v>
       </c>
       <c r="O265" t="s" s="2">
-        <v>883</v>
+        <v>867</v>
       </c>
       <c r="P265" t="s" s="2">
         <v>78</v>
@@ -34022,13 +34069,13 @@
         <v>78</v>
       </c>
       <c r="X265" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="Y265" t="s" s="2">
-        <v>884</v>
+        <v>78</v>
       </c>
       <c r="Z265" t="s" s="2">
-        <v>885</v>
+        <v>78</v>
       </c>
       <c r="AA265" t="s" s="2">
         <v>78</v>
@@ -34046,7 +34093,7 @@
         <v>78</v>
       </c>
       <c r="AF265" t="s" s="2">
-        <v>879</v>
+        <v>862</v>
       </c>
       <c r="AG265" t="s" s="2">
         <v>79</v>
@@ -34064,10 +34111,10 @@
         <v>78</v>
       </c>
       <c r="AL265" t="s" s="2">
-        <v>886</v>
+        <v>570</v>
       </c>
       <c r="AM265" t="s" s="2">
-        <v>109</v>
+        <v>571</v>
       </c>
       <c r="AN265" t="s" s="2">
         <v>78</v>
@@ -34076,12 +34123,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="266" hidden="true">
+    <row r="266">
       <c r="A266" t="s" s="2">
-        <v>887</v>
+        <v>868</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>887</v>
+        <v>868</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -34089,13 +34136,13 @@
       </c>
       <c r="E266" s="2"/>
       <c r="F266" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G266" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H266" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I266" t="s" s="2">
         <v>78</v>
@@ -34104,18 +34151,20 @@
         <v>78</v>
       </c>
       <c r="K266" t="s" s="2">
-        <v>811</v>
+        <v>237</v>
       </c>
       <c r="L266" t="s" s="2">
-        <v>888</v>
+        <v>869</v>
       </c>
       <c r="M266" t="s" s="2">
-        <v>889</v>
+        <v>870</v>
       </c>
       <c r="N266" t="s" s="2">
-        <v>890</v>
-      </c>
-      <c r="O266" s="2"/>
+        <v>871</v>
+      </c>
+      <c r="O266" t="s" s="2">
+        <v>872</v>
+      </c>
       <c r="P266" t="s" s="2">
         <v>78</v>
       </c>
@@ -34139,13 +34188,11 @@
         <v>78</v>
       </c>
       <c r="X266" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y266" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="Y266" s="2"/>
       <c r="Z266" t="s" s="2">
-        <v>78</v>
+        <v>873</v>
       </c>
       <c r="AA266" t="s" s="2">
         <v>78</v>
@@ -34163,16 +34210,16 @@
         <v>78</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>887</v>
+        <v>868</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH266" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI266" t="s" s="2">
-        <v>891</v>
+        <v>78</v>
       </c>
       <c r="AJ266" t="s" s="2">
         <v>103</v>
@@ -34181,10 +34228,10 @@
         <v>78</v>
       </c>
       <c r="AL266" t="s" s="2">
-        <v>892</v>
+        <v>471</v>
       </c>
       <c r="AM266" t="s" s="2">
-        <v>893</v>
+        <v>472</v>
       </c>
       <c r="AN266" t="s" s="2">
         <v>78</v>
@@ -34195,10 +34242,10 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>894</v>
+        <v>874</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>894</v>
+        <v>874</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -34209,7 +34256,7 @@
         <v>79</v>
       </c>
       <c r="G267" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H267" t="s" s="2">
         <v>78</v>
@@ -34221,19 +34268,17 @@
         <v>78</v>
       </c>
       <c r="K267" t="s" s="2">
-        <v>237</v>
+        <v>875</v>
       </c>
       <c r="L267" t="s" s="2">
-        <v>895</v>
+        <v>876</v>
       </c>
       <c r="M267" t="s" s="2">
-        <v>896</v>
-      </c>
-      <c r="N267" t="s" s="2">
-        <v>897</v>
-      </c>
+        <v>877</v>
+      </c>
+      <c r="N267" s="2"/>
       <c r="O267" t="s" s="2">
-        <v>898</v>
+        <v>550</v>
       </c>
       <c r="P267" t="s" s="2">
         <v>78</v>
@@ -34258,13 +34303,13 @@
         <v>78</v>
       </c>
       <c r="X267" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="Y267" t="s" s="2">
-        <v>899</v>
+        <v>78</v>
       </c>
       <c r="Z267" t="s" s="2">
-        <v>900</v>
+        <v>78</v>
       </c>
       <c r="AA267" t="s" s="2">
         <v>78</v>
@@ -34282,16 +34327,16 @@
         <v>78</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>894</v>
+        <v>874</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH267" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI267" t="s" s="2">
-        <v>891</v>
+        <v>78</v>
       </c>
       <c r="AJ267" t="s" s="2">
         <v>103</v>
@@ -34300,24 +34345,24 @@
         <v>78</v>
       </c>
       <c r="AL267" t="s" s="2">
-        <v>901</v>
+        <v>552</v>
       </c>
       <c r="AM267" t="s" s="2">
-        <v>109</v>
+        <v>553</v>
       </c>
       <c r="AN267" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO267" t="s" s="2">
-        <v>78</v>
+        <v>555</v>
       </c>
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>902</v>
+        <v>878</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>902</v>
+        <v>878</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -34328,7 +34373,7 @@
         <v>79</v>
       </c>
       <c r="G268" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H268" t="s" s="2">
         <v>78</v>
@@ -34340,16 +34385,16 @@
         <v>78</v>
       </c>
       <c r="K268" t="s" s="2">
-        <v>81</v>
+        <v>817</v>
       </c>
       <c r="L268" t="s" s="2">
-        <v>903</v>
+        <v>879</v>
       </c>
       <c r="M268" t="s" s="2">
-        <v>904</v>
+        <v>880</v>
       </c>
       <c r="N268" t="s" s="2">
-        <v>905</v>
+        <v>881</v>
       </c>
       <c r="O268" s="2"/>
       <c r="P268" t="s" s="2">
@@ -34399,16 +34444,16 @@
         <v>78</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>902</v>
+        <v>878</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH268" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI268" t="s" s="2">
-        <v>869</v>
+        <v>78</v>
       </c>
       <c r="AJ268" t="s" s="2">
         <v>103</v>
@@ -34417,20 +34462,728 @@
         <v>78</v>
       </c>
       <c r="AL268" t="s" s="2">
-        <v>831</v>
+        <v>78</v>
       </c>
       <c r="AM268" t="s" s="2">
+        <v>882</v>
+      </c>
+      <c r="AN268" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO268" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s" s="2">
+        <v>883</v>
+      </c>
+      <c r="B269" t="s" s="2">
+        <v>883</v>
+      </c>
+      <c r="C269" s="2"/>
+      <c r="D269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E269" s="2"/>
+      <c r="F269" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G269" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H269" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K269" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L269" t="s" s="2">
+        <v>884</v>
+      </c>
+      <c r="M269" t="s" s="2">
+        <v>885</v>
+      </c>
+      <c r="N269" t="s" s="2">
+        <v>886</v>
+      </c>
+      <c r="O269" s="2"/>
+      <c r="P269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q269" s="2"/>
+      <c r="R269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF269" t="s" s="2">
+        <v>883</v>
+      </c>
+      <c r="AG269" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH269" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI269" t="s" s="2">
+        <v>887</v>
+      </c>
+      <c r="AJ269" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL269" t="s" s="2">
+        <v>888</v>
+      </c>
+      <c r="AM269" t="s" s="2">
+        <v>888</v>
+      </c>
+      <c r="AN269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO269" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="270" hidden="true">
+      <c r="A270" t="s" s="2">
+        <v>889</v>
+      </c>
+      <c r="B270" t="s" s="2">
+        <v>889</v>
+      </c>
+      <c r="C270" s="2"/>
+      <c r="D270" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E270" s="2"/>
+      <c r="F270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G270" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H270" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I270" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J270" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K270" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L270" t="s" s="2">
+        <v>890</v>
+      </c>
+      <c r="M270" t="s" s="2">
+        <v>891</v>
+      </c>
+      <c r="N270" t="s" s="2">
+        <v>892</v>
+      </c>
+      <c r="O270" t="s" s="2">
+        <v>893</v>
+      </c>
+      <c r="P270" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q270" s="2"/>
+      <c r="R270" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S270" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T270" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U270" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V270" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W270" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X270" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="Y270" t="s" s="2">
+        <v>894</v>
+      </c>
+      <c r="Z270" t="s" s="2">
+        <v>895</v>
+      </c>
+      <c r="AA270" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB270" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC270" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD270" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE270" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF270" t="s" s="2">
+        <v>889</v>
+      </c>
+      <c r="AG270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH270" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI270" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ270" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK270" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL270" t="s" s="2">
+        <v>896</v>
+      </c>
+      <c r="AM270" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AN270" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO270" t="s" s="2">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="271" hidden="true">
+      <c r="A271" t="s" s="2">
+        <v>897</v>
+      </c>
+      <c r="B271" t="s" s="2">
+        <v>897</v>
+      </c>
+      <c r="C271" s="2"/>
+      <c r="D271" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E271" s="2"/>
+      <c r="F271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G271" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H271" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I271" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J271" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K271" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L271" t="s" s="2">
+        <v>898</v>
+      </c>
+      <c r="M271" t="s" s="2">
+        <v>899</v>
+      </c>
+      <c r="N271" t="s" s="2">
+        <v>900</v>
+      </c>
+      <c r="O271" t="s" s="2">
+        <v>901</v>
+      </c>
+      <c r="P271" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q271" s="2"/>
+      <c r="R271" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S271" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T271" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U271" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V271" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W271" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X271" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Y271" t="s" s="2">
+        <v>902</v>
+      </c>
+      <c r="Z271" t="s" s="2">
+        <v>903</v>
+      </c>
+      <c r="AA271" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB271" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC271" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD271" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE271" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF271" t="s" s="2">
+        <v>897</v>
+      </c>
+      <c r="AG271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH271" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI271" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ271" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK271" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL271" t="s" s="2">
+        <v>904</v>
+      </c>
+      <c r="AM271" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AN271" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO271" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="272" hidden="true">
+      <c r="A272" t="s" s="2">
+        <v>905</v>
+      </c>
+      <c r="B272" t="s" s="2">
+        <v>905</v>
+      </c>
+      <c r="C272" s="2"/>
+      <c r="D272" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E272" s="2"/>
+      <c r="F272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G272" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H272" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I272" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J272" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K272" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="L272" t="s" s="2">
         <v>906</v>
       </c>
-      <c r="AN268" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO268" t="s" s="2">
+      <c r="M272" t="s" s="2">
+        <v>907</v>
+      </c>
+      <c r="N272" t="s" s="2">
+        <v>908</v>
+      </c>
+      <c r="O272" s="2"/>
+      <c r="P272" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q272" s="2"/>
+      <c r="R272" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S272" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T272" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U272" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V272" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W272" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X272" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y272" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z272" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA272" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB272" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC272" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD272" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE272" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF272" t="s" s="2">
+        <v>905</v>
+      </c>
+      <c r="AG272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH272" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI272" t="s" s="2">
+        <v>909</v>
+      </c>
+      <c r="AJ272" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK272" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL272" t="s" s="2">
+        <v>910</v>
+      </c>
+      <c r="AM272" t="s" s="2">
+        <v>911</v>
+      </c>
+      <c r="AN272" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO272" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="273" hidden="true">
+      <c r="A273" t="s" s="2">
+        <v>912</v>
+      </c>
+      <c r="B273" t="s" s="2">
+        <v>912</v>
+      </c>
+      <c r="C273" s="2"/>
+      <c r="D273" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E273" s="2"/>
+      <c r="F273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G273" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H273" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I273" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J273" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K273" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L273" t="s" s="2">
+        <v>913</v>
+      </c>
+      <c r="M273" t="s" s="2">
+        <v>914</v>
+      </c>
+      <c r="N273" t="s" s="2">
+        <v>915</v>
+      </c>
+      <c r="O273" t="s" s="2">
+        <v>916</v>
+      </c>
+      <c r="P273" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q273" s="2"/>
+      <c r="R273" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S273" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T273" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U273" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V273" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W273" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X273" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Y273" t="s" s="2">
+        <v>917</v>
+      </c>
+      <c r="Z273" t="s" s="2">
+        <v>918</v>
+      </c>
+      <c r="AA273" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB273" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC273" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD273" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE273" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF273" t="s" s="2">
+        <v>912</v>
+      </c>
+      <c r="AG273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH273" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI273" t="s" s="2">
+        <v>909</v>
+      </c>
+      <c r="AJ273" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK273" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL273" t="s" s="2">
+        <v>919</v>
+      </c>
+      <c r="AM273" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AN273" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO273" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="274" hidden="true">
+      <c r="A274" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="B274" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="C274" s="2"/>
+      <c r="D274" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E274" s="2"/>
+      <c r="F274" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G274" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H274" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I274" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J274" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K274" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="L274" t="s" s="2">
+        <v>921</v>
+      </c>
+      <c r="M274" t="s" s="2">
+        <v>922</v>
+      </c>
+      <c r="N274" t="s" s="2">
+        <v>923</v>
+      </c>
+      <c r="O274" s="2"/>
+      <c r="P274" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q274" s="2"/>
+      <c r="R274" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S274" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T274" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U274" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V274" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W274" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X274" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y274" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z274" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA274" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB274" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC274" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD274" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE274" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF274" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="AG274" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH274" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI274" t="s" s="2">
+        <v>887</v>
+      </c>
+      <c r="AJ274" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK274" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL274" t="s" s="2">
+        <v>849</v>
+      </c>
+      <c r="AM274" t="s" s="2">
+        <v>924</v>
+      </c>
+      <c r="AN274" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO274" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO268">
+  <autoFilter ref="A1:AO274">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -34440,7 +35193,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI267">
+  <conditionalFormatting sqref="A2:AI273">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:06:50+00:00</t>
+    <t>2026-10-01T08:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10109" uniqueCount="925">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10108" uniqueCount="927">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T08:49:37+00:00</t>
+    <t>2026-10-01T13:34:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -897,7 +897,7 @@
 </t>
   </si>
   <si>
-    <t>Informant Extension</t>
+    <t>Informateur</t>
   </si>
   <si>
     <t>Informant Extension describes an information source for any content within the clinical document. This informant is constrained for use when the source of information is an assigned health care provider for the patient.</t>
@@ -978,9 +978,6 @@
     <t>Composition.extension:informant.extension:party</t>
   </si>
   <si>
-    <t>Informateur</t>
-  </si>
-  <si>
     <t>Composition.extension:informant.extension:party.id</t>
   </si>
   <si>
@@ -1257,7 +1254,7 @@
 </t>
   </si>
   <si>
-    <t>Fulfills plan, proposal or order</t>
+    <t>Prescription ou Plan</t>
   </si>
   <si>
     <t>A plan, proposal or order that is fulfilled in whole or in part by this event.</t>
@@ -1284,11 +1281,11 @@
     <t>Composition.extension:basedOn.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-service-request-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-care-plan-document|0.1.0)
 </t>
   </si>
   <si>
-    <t>Association du document à une prescription</t>
+    <t>Association du document à une prescription ou un plan</t>
   </si>
   <si>
     <t>Composition.extension:change-made</t>
@@ -1512,7 +1509,7 @@
     <t>Composition.category</t>
   </si>
   <si>
-    <t>Categorization of Composition</t>
+    <t>Catégorie du document</t>
   </si>
   <si>
     <t>A categorization for the type of the composition - helps for indexing and searching. This may be implied by or derived from the code specified in the Composition Type.</t>
@@ -1524,10 +1521,7 @@
     <t>Helps humans to assess whether the composition is of interest when viewing an index of compositions or documents.</t>
   </si>
   <si>
-    <t>High-level kind of a clinical document at a macro level.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/document-classcodes|4.0.1</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J06-XdsClassCode-CISIS/FHIR/JDV-J06-XdsClassCode-CISIS|20230922120000</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1557,6 +1551,12 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>High-level kind of a clinical document at a macro level.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/document-classcodes|4.0.1</t>
+  </si>
+  <si>
     <t>Composition.subject</t>
   </si>
   <si>
@@ -2589,6 +2589,9 @@
     <t>Composition.event:principalEvent.id</t>
   </si>
   <si>
+    <t>Identifiant de l'évènement documenté</t>
+  </si>
+  <si>
     <t>Composition.event:principalEvent.extension</t>
   </si>
   <si>
@@ -2639,6 +2642,9 @@
   </si>
   <si>
     <t>Composition.event:principalEvent.code</t>
+  </si>
+  <si>
+    <t>Code de l'évènement documenté</t>
   </si>
   <si>
     <t>Composition.event:principalEvent.period</t>
@@ -3239,7 +3245,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="89.12890625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="89.64453125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="101.734375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -3615,7 +3621,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>98</v>
       </c>
@@ -3628,13 +3634,13 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>78</v>
@@ -4326,13 +4332,13 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>78</v>
@@ -4445,7 +4451,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>91</v>
@@ -10727,7 +10733,7 @@
         <v>112</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="M65" t="s" s="2">
         <v>200</v>
@@ -10813,7 +10819,7 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>226</v>
@@ -10928,7 +10934,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>228</v>
@@ -11043,7 +11049,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>230</v>
@@ -11160,7 +11166,7 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>236</v>
@@ -11186,7 +11192,7 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>238</v>
@@ -11275,7 +11281,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>271</v>
@@ -11318,7 +11324,7 @@
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>78</v>
@@ -11392,7 +11398,7 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>274</v>
@@ -11507,19 +11513,19 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>198</v>
       </c>
       <c r="C72" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="D72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E72" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="D72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E72" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="F72" t="s" s="2">
         <v>79</v>
@@ -11537,13 +11543,13 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11626,7 +11632,7 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>218</v>
@@ -11741,7 +11747,7 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>220</v>
@@ -11856,7 +11862,7 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>220</v>
@@ -11887,7 +11893,7 @@
         <v>112</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M75" t="s" s="2">
         <v>200</v>
@@ -11973,7 +11979,7 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>226</v>
@@ -12088,7 +12094,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>228</v>
@@ -12203,7 +12209,7 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>230</v>
@@ -12320,7 +12326,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>236</v>
@@ -12379,11 +12385,11 @@
         <v>78</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>78</v>
@@ -12433,7 +12439,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>220</v>
@@ -12550,7 +12556,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>226</v>
@@ -12665,7 +12671,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>228</v>
@@ -12780,7 +12786,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>230</v>
@@ -12897,7 +12903,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>236</v>
@@ -13010,7 +13016,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>220</v>
@@ -13127,7 +13133,7 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>226</v>
@@ -13242,7 +13248,7 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>228</v>
@@ -13357,7 +13363,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>230</v>
@@ -13474,7 +13480,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>236</v>
@@ -13589,7 +13595,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>220</v>
@@ -13620,7 +13626,7 @@
         <v>112</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M90" t="s" s="2">
         <v>200</v>
@@ -13706,7 +13712,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>226</v>
@@ -13821,7 +13827,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>228</v>
@@ -13936,7 +13942,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>230</v>
@@ -14053,7 +14059,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>236</v>
@@ -14168,7 +14174,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>271</v>
@@ -14211,7 +14217,7 @@
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="S95" t="s" s="2">
         <v>78</v>
@@ -14285,7 +14291,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>274</v>
@@ -14400,19 +14406,19 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>198</v>
       </c>
       <c r="C97" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="D97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E97" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="D97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E97" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="F97" t="s" s="2">
         <v>79</v>
@@ -14430,13 +14436,13 @@
         <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14519,7 +14525,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>218</v>
@@ -14634,7 +14640,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>220</v>
@@ -14749,7 +14755,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>220</v>
@@ -14780,7 +14786,7 @@
         <v>112</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="M100" t="s" s="2">
         <v>200</v>
@@ -14866,7 +14872,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>226</v>
@@ -14981,7 +14987,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>228</v>
@@ -15096,7 +15102,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>230</v>
@@ -15213,7 +15219,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>236</v>
@@ -15272,11 +15278,11 @@
         <v>78</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>78</v>
@@ -15326,7 +15332,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>220</v>
@@ -15357,7 +15363,7 @@
         <v>112</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="M105" t="s" s="2">
         <v>200</v>
@@ -15443,7 +15449,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>226</v>
@@ -15558,7 +15564,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>228</v>
@@ -15673,7 +15679,7 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>230</v>
@@ -15790,7 +15796,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>236</v>
@@ -15849,11 +15855,11 @@
         <v>78</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y109" s="2"/>
       <c r="Z109" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>78</v>
@@ -15903,7 +15909,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>220</v>
@@ -15934,7 +15940,7 @@
         <v>112</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="M110" t="s" s="2">
         <v>200</v>
@@ -16020,7 +16026,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>226</v>
@@ -16135,7 +16141,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>228</v>
@@ -16250,7 +16256,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>230</v>
@@ -16367,7 +16373,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>236</v>
@@ -16482,7 +16488,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>220</v>
@@ -16513,7 +16519,7 @@
         <v>112</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M115" t="s" s="2">
         <v>200</v>
@@ -16579,7 +16585,7 @@
         <v>78</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>78</v>
@@ -16599,7 +16605,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>226</v>
@@ -16714,7 +16720,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>228</v>
@@ -16829,7 +16835,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>230</v>
@@ -16946,7 +16952,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>236</v>
@@ -17061,7 +17067,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>271</v>
@@ -17104,7 +17110,7 @@
       </c>
       <c r="Q120" s="2"/>
       <c r="R120" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="S120" t="s" s="2">
         <v>78</v>
@@ -17178,7 +17184,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>274</v>
@@ -17293,19 +17299,19 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>198</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E122" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F122" t="s" s="2">
         <v>79</v>
@@ -17323,13 +17329,13 @@
         <v>78</v>
       </c>
       <c r="K122" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L122" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L122" t="s" s="2">
+      <c r="M122" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17412,19 +17418,19 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>198</v>
       </c>
       <c r="C123" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="D123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E123" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="D123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E123" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="F123" t="s" s="2">
         <v>79</v>
@@ -17442,13 +17448,13 @@
         <v>78</v>
       </c>
       <c r="K123" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L123" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="L123" t="s" s="2">
+      <c r="M123" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -17514,10 +17520,10 @@
         <v>120</v>
       </c>
       <c r="AK123" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AL123" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>78</v>
@@ -17531,7 +17537,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>218</v>
@@ -17646,7 +17652,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>220</v>
@@ -17761,7 +17767,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>271</v>
@@ -17804,7 +17810,7 @@
       </c>
       <c r="Q126" s="2"/>
       <c r="R126" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="S126" t="s" s="2">
         <v>78</v>
@@ -17878,7 +17884,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>274</v>
@@ -17904,10 +17910,10 @@
         <v>78</v>
       </c>
       <c r="K127" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L127" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="L127" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="M127" t="s" s="2">
         <v>239</v>
@@ -17993,43 +17999,43 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>198</v>
       </c>
       <c r="C128" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="D128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E128" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="D128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E128" t="s" s="2">
+      <c r="F128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K128" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="F128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G128" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K128" t="s" s="2">
+      <c r="L128" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="L128" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -18112,13 +18118,13 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>198</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>78</v>
@@ -18140,13 +18146,13 @@
         <v>78</v>
       </c>
       <c r="K129" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L129" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="L129" t="s" s="2">
+      <c r="M129" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -18229,7 +18235,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>218</v>
@@ -18344,7 +18350,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>220</v>
@@ -18459,7 +18465,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>271</v>
@@ -18502,7 +18508,7 @@
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>78</v>
@@ -18576,7 +18582,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>274</v>
@@ -18602,13 +18608,13 @@
         <v>78</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L133" t="s" s="2">
         <v>238</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -18668,7 +18674,7 @@
         <v>91</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>103</v>
@@ -18691,10 +18697,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18720,16 +18726,16 @@
         <v>112</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="N134" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>78</v>
@@ -18778,7 +18784,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18810,10 +18816,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18836,16 +18842,16 @@
         <v>92</v>
       </c>
       <c r="K135" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L135" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="L135" t="s" s="2">
+      <c r="M135" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18895,7 +18901,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18910,27 +18916,27 @@
         <v>103</v>
       </c>
       <c r="AK135" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AL135" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AL135" t="s" s="2">
+      <c r="AM135" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="AM135" t="s" s="2">
+      <c r="AN135" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AN135" t="s" s="2">
+      <c r="AO135" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AO135" t="s" s="2">
-        <v>438</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18956,16 +18962,16 @@
         <v>173</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="N136" t="s" s="2">
+      <c r="O136" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>78</v>
@@ -18990,14 +18996,14 @@
         <v>78</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y136" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="Z136" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="Z136" t="s" s="2">
-        <v>445</v>
-      </c>
       <c r="AA136" t="s" s="2">
         <v>78</v>
       </c>
@@ -19014,7 +19020,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>91</v>
@@ -19029,27 +19035,27 @@
         <v>103</v>
       </c>
       <c r="AK136" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AL136" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AL136" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AN136" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AO136" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="AO136" t="s" s="2">
-        <v>449</v>
       </c>
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19075,10 +19081,10 @@
         <v>105</v>
       </c>
       <c r="L137" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M137" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -19161,10 +19167,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19274,13 +19280,13 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C139" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C139" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>78</v>
@@ -19302,16 +19308,16 @@
         <v>78</v>
       </c>
       <c r="K139" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="L139" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="L139" t="s" s="2">
+      <c r="M139" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M139" t="s" s="2">
+      <c r="N139" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -19393,10 +19399,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19422,10 +19428,10 @@
         <v>105</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -19476,7 +19482,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -19508,10 +19514,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19537,16 +19543,16 @@
         <v>237</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="M141" t="s" s="2">
+      <c r="N141" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="N141" t="s" s="2">
+      <c r="O141" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>78</v>
@@ -19574,11 +19580,11 @@
         <v>177</v>
       </c>
       <c r="Y141" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="Z141" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="Z141" t="s" s="2">
-        <v>469</v>
-      </c>
       <c r="AA141" t="s" s="2">
         <v>78</v>
       </c>
@@ -19595,7 +19601,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>91</v>
@@ -19610,27 +19616,27 @@
         <v>103</v>
       </c>
       <c r="AK141" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AL141" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AL141" t="s" s="2">
+      <c r="AM141" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AM141" t="s" s="2">
+      <c r="AN141" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AN141" t="s" s="2">
+      <c r="AO141" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AO141" t="s" s="2">
-        <v>474</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19656,16 +19662,16 @@
         <v>237</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="M142" t="s" s="2">
+      <c r="N142" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="N142" t="s" s="2">
+      <c r="O142" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>78</v>
@@ -19690,13 +19696,11 @@
         <v>78</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>480</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y142" s="2"/>
       <c r="Z142" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>78</v>
@@ -19712,7 +19716,7 @@
         <v>118</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19727,30 +19731,30 @@
         <v>103</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D143" t="s" s="2">
         <v>78</v>
@@ -19775,16 +19779,16 @@
         <v>237</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="M143" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N143" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="N143" t="s" s="2">
+      <c r="O143" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>78</v>
@@ -19794,7 +19798,7 @@
         <v>78</v>
       </c>
       <c r="S143" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="T143" t="s" s="2">
         <v>78</v>
@@ -19812,10 +19816,10 @@
         <v>163</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>78</v>
@@ -19833,7 +19837,7 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19848,19 +19852,19 @@
         <v>103</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="144">
@@ -20476,7 +20480,7 @@
         <v>92</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L149" t="s" s="2">
         <v>515</v>
@@ -21644,7 +21648,7 @@
         <v>92</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L159" t="s" s="2">
         <v>515</v>
@@ -22030,7 +22034,7 @@
         <v>78</v>
       </c>
       <c r="X162" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y162" t="s" s="2">
         <v>577</v>
@@ -22475,7 +22479,7 @@
         <v>115</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>78</v>
@@ -22617,7 +22621,7 @@
         <v>78</v>
       </c>
       <c r="X167" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y167" t="s" s="2">
         <v>603</v>
@@ -23298,7 +23302,7 @@
         <v>115</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>78</v>
@@ -23440,7 +23444,7 @@
         <v>78</v>
       </c>
       <c r="X174" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y174" t="s" s="2">
         <v>603</v>
@@ -24121,7 +24125,7 @@
         <v>115</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>78</v>
@@ -24263,7 +24267,7 @@
         <v>78</v>
       </c>
       <c r="X181" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y181" t="s" s="2">
         <v>603</v>
@@ -25059,7 +25063,7 @@
         <v>115</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>78</v>
@@ -25201,7 +25205,7 @@
         <v>78</v>
       </c>
       <c r="X189" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y189" t="s" s="2">
         <v>666</v>
@@ -25398,7 +25402,7 @@
         <v>78</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L191" t="s" s="2">
         <v>680</v>
@@ -25782,7 +25786,7 @@
         <v>78</v>
       </c>
       <c r="X194" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y194" t="s" s="2">
         <v>691</v>
@@ -26814,7 +26818,7 @@
         <v>115</v>
       </c>
       <c r="O203" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>78</v>
@@ -26956,7 +26960,7 @@
         <v>78</v>
       </c>
       <c r="X204" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y204" t="s" s="2">
         <v>666</v>
@@ -27038,7 +27042,7 @@
         <v>78</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L205" t="s" s="2">
         <v>673</v>
@@ -27153,7 +27157,7 @@
         <v>78</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L206" t="s" s="2">
         <v>745</v>
@@ -27537,7 +27541,7 @@
         <v>78</v>
       </c>
       <c r="X209" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y209" t="s" s="2">
         <v>691</v>
@@ -28569,7 +28573,7 @@
         <v>115</v>
       </c>
       <c r="O218" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P218" t="s" s="2">
         <v>78</v>
@@ -28711,7 +28715,7 @@
         <v>78</v>
       </c>
       <c r="X219" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y219" t="s" s="2">
         <v>666</v>
@@ -28793,7 +28797,7 @@
         <v>78</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L220" t="s" s="2">
         <v>673</v>
@@ -28908,7 +28912,7 @@
         <v>78</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L221" t="s" s="2">
         <v>673</v>
@@ -29292,7 +29296,7 @@
         <v>78</v>
       </c>
       <c r="X224" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y224" t="s" s="2">
         <v>691</v>
@@ -30324,7 +30328,7 @@
         <v>115</v>
       </c>
       <c r="O233" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P233" t="s" s="2">
         <v>78</v>
@@ -30466,7 +30470,7 @@
         <v>78</v>
       </c>
       <c r="X234" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y234" t="s" s="2">
         <v>666</v>
@@ -30663,7 +30667,7 @@
         <v>78</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L236" t="s" s="2">
         <v>680</v>
@@ -31369,7 +31373,7 @@
         <v>115</v>
       </c>
       <c r="O242" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P242" t="s" s="2">
         <v>78</v>
@@ -31553,10 +31557,10 @@
         <v>78</v>
       </c>
       <c r="AL243" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AM243" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AN243" t="s" s="2">
         <v>811</v>
@@ -31696,7 +31700,7 @@
         <v>79</v>
       </c>
       <c r="G245" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H245" t="s" s="2">
         <v>78</v>
@@ -31947,7 +31951,7 @@
         <v>105</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>106</v>
+        <v>825</v>
       </c>
       <c r="M247" t="s" s="2">
         <v>107</v>
@@ -32033,7 +32037,7 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B248" t="s" s="2">
         <v>793</v>
@@ -32146,7 +32150,7 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B249" t="s" s="2">
         <v>793</v>
@@ -32177,7 +32181,7 @@
         <v>796</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="M249" t="s" s="2">
         <v>798</v>
@@ -32263,7 +32267,7 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B250" t="s" s="2">
         <v>793</v>
@@ -32380,10 +32384,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -32495,10 +32499,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -32610,10 +32614,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -32653,7 +32657,7 @@
       </c>
       <c r="Q253" s="2"/>
       <c r="R253" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="S253" t="s" s="2">
         <v>78</v>
@@ -32727,10 +32731,10 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -32753,7 +32757,7 @@
         <v>78</v>
       </c>
       <c r="K254" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="L254" t="s" s="2">
         <v>238</v>
@@ -32771,7 +32775,7 @@
         <v>78</v>
       </c>
       <c r="S254" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="T254" t="s" s="2">
         <v>78</v>
@@ -32842,7 +32846,7 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B255" t="s" s="2">
         <v>804</v>
@@ -32880,7 +32884,7 @@
         <v>115</v>
       </c>
       <c r="O255" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P255" t="s" s="2">
         <v>78</v>
@@ -32961,7 +32965,7 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B256" t="s" s="2">
         <v>805</v>
@@ -32990,7 +32994,7 @@
         <v>237</v>
       </c>
       <c r="L256" t="s" s="2">
-        <v>806</v>
+        <v>843</v>
       </c>
       <c r="M256" t="s" s="2">
         <v>807</v>
@@ -33064,10 +33068,10 @@
         <v>78</v>
       </c>
       <c r="AL256" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AM256" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AN256" t="s" s="2">
         <v>811</v>
@@ -33078,7 +33082,7 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B257" t="s" s="2">
         <v>812</v>
@@ -33107,7 +33111,7 @@
         <v>261</v>
       </c>
       <c r="L257" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="M257" t="s" s="2">
         <v>814</v>
@@ -33193,7 +33197,7 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B258" t="s" s="2">
         <v>816</v>
@@ -33207,7 +33211,7 @@
         <v>79</v>
       </c>
       <c r="G258" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H258" t="s" s="2">
         <v>78</v>
@@ -33308,10 +33312,10 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -33337,10 +33341,10 @@
         <v>582</v>
       </c>
       <c r="L259" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="M259" t="s" s="2">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="N259" s="2"/>
       <c r="O259" s="2"/>
@@ -33391,7 +33395,7 @@
         <v>78</v>
       </c>
       <c r="AF259" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="AG259" t="s" s="2">
         <v>79</v>
@@ -33403,16 +33407,16 @@
         <v>78</v>
       </c>
       <c r="AJ259" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="AK259" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL259" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="AM259" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="AN259" t="s" s="2">
         <v>78</v>
@@ -33423,10 +33427,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -33538,10 +33542,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -33651,13 +33655,13 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C262" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D262" t="s" s="2">
         <v>78</v>
@@ -33679,13 +33683,13 @@
         <v>78</v>
       </c>
       <c r="K262" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L262" t="s" s="2">
+        <v>856</v>
+      </c>
+      <c r="M262" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="L262" t="s" s="2">
-        <v>854</v>
-      </c>
-      <c r="M262" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="N262" s="2"/>
       <c r="O262" s="2"/>
@@ -33768,13 +33772,13 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="D263" t="s" s="2">
         <v>78</v>
@@ -33796,16 +33800,16 @@
         <v>78</v>
       </c>
       <c r="K263" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="N263" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="O263" s="2"/>
       <c r="P263" t="s" s="2">
@@ -33887,10 +33891,10 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -33925,7 +33929,7 @@
         <v>115</v>
       </c>
       <c r="O264" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P264" t="s" s="2">
         <v>78</v>
@@ -34006,14 +34010,14 @@
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="E265" s="2"/>
       <c r="F265" t="s" s="2">
@@ -34035,16 +34039,16 @@
         <v>105</v>
       </c>
       <c r="L265" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="M265" t="s" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="N265" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="O265" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="P265" t="s" s="2">
         <v>78</v>
@@ -34093,7 +34097,7 @@
         <v>78</v>
       </c>
       <c r="AF265" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="AG265" t="s" s="2">
         <v>79</v>
@@ -34125,10 +34129,10 @@
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -34154,16 +34158,16 @@
         <v>237</v>
       </c>
       <c r="L266" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="M266" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="N266" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="O266" t="s" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="P266" t="s" s="2">
         <v>78</v>
@@ -34188,11 +34192,11 @@
         <v>78</v>
       </c>
       <c r="X266" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y266" s="2"/>
       <c r="Z266" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="AA266" t="s" s="2">
         <v>78</v>
@@ -34210,7 +34214,7 @@
         <v>78</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>79</v>
@@ -34228,10 +34232,10 @@
         <v>78</v>
       </c>
       <c r="AL266" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AM266" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AM266" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="AN266" t="s" s="2">
         <v>78</v>
@@ -34242,10 +34246,10 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -34268,13 +34272,13 @@
         <v>78</v>
       </c>
       <c r="K267" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="L267" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="M267" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="N267" s="2"/>
       <c r="O267" t="s" s="2">
@@ -34327,7 +34331,7 @@
         <v>78</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>79</v>
@@ -34359,10 +34363,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -34388,13 +34392,13 @@
         <v>817</v>
       </c>
       <c r="L268" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="M268" t="s" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="N268" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="O268" s="2"/>
       <c r="P268" t="s" s="2">
@@ -34444,7 +34448,7 @@
         <v>78</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>79</v>
@@ -34465,7 +34469,7 @@
         <v>78</v>
       </c>
       <c r="AM268" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="AN268" t="s" s="2">
         <v>78</v>
@@ -34476,10 +34480,10 @@
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -34505,13 +34509,13 @@
         <v>184</v>
       </c>
       <c r="L269" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="M269" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="N269" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="O269" s="2"/>
       <c r="P269" t="s" s="2">
@@ -34561,7 +34565,7 @@
         <v>78</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>79</v>
@@ -34570,7 +34574,7 @@
         <v>91</v>
       </c>
       <c r="AI269" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="AJ269" t="s" s="2">
         <v>103</v>
@@ -34579,10 +34583,10 @@
         <v>78</v>
       </c>
       <c r="AL269" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="AM269" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="AN269" t="s" s="2">
         <v>78</v>
@@ -34593,10 +34597,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -34622,16 +34626,16 @@
         <v>173</v>
       </c>
       <c r="L270" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="M270" t="s" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="N270" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="O270" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="P270" t="s" s="2">
         <v>78</v>
@@ -34656,13 +34660,13 @@
         <v>78</v>
       </c>
       <c r="X270" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Y270" t="s" s="2">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="Z270" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="AA270" t="s" s="2">
         <v>78</v>
@@ -34680,7 +34684,7 @@
         <v>78</v>
       </c>
       <c r="AF270" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="AG270" t="s" s="2">
         <v>79</v>
@@ -34698,7 +34702,7 @@
         <v>78</v>
       </c>
       <c r="AL270" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="AM270" t="s" s="2">
         <v>109</v>
@@ -34707,15 +34711,15 @@
         <v>78</v>
       </c>
       <c r="AO270" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -34741,16 +34745,16 @@
         <v>237</v>
       </c>
       <c r="L271" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="M271" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="N271" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="O271" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="P271" t="s" s="2">
         <v>78</v>
@@ -34778,10 +34782,10 @@
         <v>177</v>
       </c>
       <c r="Y271" t="s" s="2">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="Z271" t="s" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="AA271" t="s" s="2">
         <v>78</v>
@@ -34799,7 +34803,7 @@
         <v>78</v>
       </c>
       <c r="AF271" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="AG271" t="s" s="2">
         <v>79</v>
@@ -34817,7 +34821,7 @@
         <v>78</v>
       </c>
       <c r="AL271" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="AM271" t="s" s="2">
         <v>109</v>
@@ -34831,10 +34835,10 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -34860,13 +34864,13 @@
         <v>817</v>
       </c>
       <c r="L272" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="M272" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="N272" t="s" s="2">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="O272" s="2"/>
       <c r="P272" t="s" s="2">
@@ -34916,7 +34920,7 @@
         <v>78</v>
       </c>
       <c r="AF272" t="s" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="AG272" t="s" s="2">
         <v>79</v>
@@ -34925,7 +34929,7 @@
         <v>80</v>
       </c>
       <c r="AI272" t="s" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="AJ272" t="s" s="2">
         <v>103</v>
@@ -34934,10 +34938,10 @@
         <v>78</v>
       </c>
       <c r="AL272" t="s" s="2">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="AM272" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="AN272" t="s" s="2">
         <v>78</v>
@@ -34948,10 +34952,10 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -34977,16 +34981,16 @@
         <v>237</v>
       </c>
       <c r="L273" t="s" s="2">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="M273" t="s" s="2">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="N273" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="O273" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="P273" t="s" s="2">
         <v>78</v>
@@ -35014,10 +35018,10 @@
         <v>177</v>
       </c>
       <c r="Y273" t="s" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="Z273" t="s" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="AA273" t="s" s="2">
         <v>78</v>
@@ -35035,7 +35039,7 @@
         <v>78</v>
       </c>
       <c r="AF273" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="AG273" t="s" s="2">
         <v>79</v>
@@ -35044,7 +35048,7 @@
         <v>91</v>
       </c>
       <c r="AI273" t="s" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="AJ273" t="s" s="2">
         <v>103</v>
@@ -35053,7 +35057,7 @@
         <v>78</v>
       </c>
       <c r="AL273" t="s" s="2">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="AM273" t="s" s="2">
         <v>109</v>
@@ -35067,10 +35071,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
@@ -35096,13 +35100,13 @@
         <v>81</v>
       </c>
       <c r="L274" t="s" s="2">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="M274" t="s" s="2">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="N274" t="s" s="2">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="O274" s="2"/>
       <c r="P274" t="s" s="2">
@@ -35152,7 +35156,7 @@
         <v>78</v>
       </c>
       <c r="AF274" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="AG274" t="s" s="2">
         <v>79</v>
@@ -35161,7 +35165,7 @@
         <v>80</v>
       </c>
       <c r="AI274" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="AJ274" t="s" s="2">
         <v>103</v>
@@ -35170,10 +35174,10 @@
         <v>78</v>
       </c>
       <c r="AL274" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="AM274" t="s" s="2">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="AN274" t="s" s="2">
         <v>78</v>
